--- a/rapporten/prijsrapport-NL-2026-07-06.xlsx
+++ b/rapporten/prijsrapport-NL-2026-07-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="138">
   <si>
     <t>Product</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>8721055499473</t>
+  </si>
+  <si>
+    <t>NG - BLUE EGAN - 100ml Eau de Toilette for Men</t>
   </si>
   <si>
     <t>8718421830015</t>
@@ -2443,7 +2446,7 @@
         <v>135</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C63" s="1">
         <v>12.5</v>
@@ -2455,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G63" s="1">
         <v>12.5</v>
